--- a/elite-data/manifest-templates/EL_template_AnalysisResultsMetadataTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AnalysisResultsMetadataTemplate.xlsx
@@ -382,13 +382,13 @@
     <t>polygenic risk scores</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>bisulfiteSeq</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>Blood Chemistry Measurement</t>
@@ -418,7 +418,7 @@
     <t>CITESeq</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>contextual conditioning behavior</t>
